--- a/artfynd/A 57295-2022 artfynd.xlsx
+++ b/artfynd/A 57295-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57295-2022 artfynd.xlsx
+++ b/artfynd/A 57295-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3298,131 +3298,6 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>107079091</v>
-      </c>
-      <c r="B24" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Hammarhön Lien, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>447382.0437725603</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7053030.842620425</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57295-2022 artfynd.xlsx
+++ b/artfynd/A 57295-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107079090</v>
+        <v>107079109</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hammarhön Lien, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447407.0631002485</v>
+        <v>447047</v>
       </c>
       <c r="R2" t="n">
-        <v>7053034.43384506</v>
+        <v>7052931</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,24 +743,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,61 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107079084</v>
+        <v>1850978</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hammarhön Lien, Jmt</t>
+          <t>Ö OM HAMMARHÖN (20E1b02), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447100.366701021</v>
+        <v>447417</v>
       </c>
       <c r="R3" t="n">
-        <v>7052951.398055498</v>
+        <v>7053162</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,27 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-09-16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>200411021 / ALE SARM / Allmän-riklig (3)  / OBJ.AREA:0,5 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,74 +858,75 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Gransumpskog /</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gammal grov gran</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Barbro Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107079096</v>
+        <v>107079104</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hammarhön Lien, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447150.700678622</v>
+        <v>447238</v>
       </c>
       <c r="R4" t="n">
-        <v>7052842.390788953</v>
+        <v>7053201</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,24 +956,14 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>måttligt - rikligt i området</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,37 +990,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107079102</v>
+        <v>107079105</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447013.088667208</v>
+        <v>447584</v>
       </c>
       <c r="R5" t="n">
-        <v>7052956.415454653</v>
+        <v>7053304</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,19 +1058,14 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>måttligt - rikligt i området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,58 +1092,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107079085</v>
+        <v>107079106</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hammarhön Lien, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447017.3291547247</v>
+        <v>447297</v>
       </c>
       <c r="R6" t="n">
-        <v>7052943.435843051</v>
+        <v>7052931</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,24 +1160,14 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>måttligt - rikligt i området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,37 +1194,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107079101</v>
+        <v>107079107</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1327,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447046.553126426</v>
+        <v>447209</v>
       </c>
       <c r="R7" t="n">
-        <v>7052931.819659834</v>
+        <v>7052872</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,19 +1262,14 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>måttligt - rikligt i området</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,12 +1299,7 @@
         <v>107079099</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447164.2208267314</v>
+        <v>447164</v>
       </c>
       <c r="R8" t="n">
-        <v>7052958.346412874</v>
+        <v>7052959</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,19 +1364,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,15 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107079089</v>
+        <v>107079100</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,38 +1404,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hammarhön Lien, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447421.8749889247</v>
+        <v>447059</v>
       </c>
       <c r="R9" t="n">
-        <v>7053067.571953109</v>
+        <v>7052937</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,24 +1461,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,15 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107079087</v>
+        <v>107079101</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,38 +1501,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hammarhön Lien, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447661.4828177911</v>
+        <v>447047</v>
       </c>
       <c r="R10" t="n">
-        <v>7053164.648952423</v>
+        <v>7052932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,24 +1558,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,15 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107079093</v>
+        <v>107079102</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,38 +1598,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hammarhön Lien, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447256.960620073</v>
+        <v>447013</v>
       </c>
       <c r="R11" t="n">
-        <v>7052906.503469526</v>
+        <v>7052957</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,24 +1655,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,15 +1684,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107079105</v>
+        <v>107079082</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,34 +1695,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hammarhön Lien, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447583.5521342007</v>
+        <v>447169</v>
       </c>
       <c r="R12" t="n">
-        <v>7053303.467789496</v>
+        <v>7052890</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1947,24 +1756,14 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>måttligt - rikligt i området</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,15 +1790,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107079104</v>
+        <v>107079083</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,34 +1801,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hammarhön Lien, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447238.2352511985</v>
+        <v>447193</v>
       </c>
       <c r="R13" t="n">
-        <v>7053201.035971886</v>
+        <v>7052953</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2064,24 +1862,14 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>måttligt - rikligt i området</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,15 +1896,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107079094</v>
+        <v>107079084</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +1927,11 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2152,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447236.1223422008</v>
+        <v>447100</v>
       </c>
       <c r="R14" t="n">
-        <v>7052886.373619192</v>
+        <v>7052952</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2185,19 +1972,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2229,15 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107079106</v>
+        <v>107079085</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,34 +2017,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarhön Lien, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447297.4864704381</v>
+        <v>447018</v>
       </c>
       <c r="R15" t="n">
-        <v>7052931.202697509</v>
+        <v>7052944</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,24 +2082,14 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>måttligt - rikligt i området</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2346,50 +2116,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107079109</v>
+        <v>107079086</v>
       </c>
       <c r="B16" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hammarhön Lien, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447046.5382724751</v>
+        <v>447522</v>
       </c>
       <c r="R16" t="n">
-        <v>7052930.929640972</v>
+        <v>7053323</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2419,19 +2188,14 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2458,15 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107079083</v>
+        <v>107079087</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447193.0958530584</v>
+        <v>447661</v>
       </c>
       <c r="R17" t="n">
-        <v>7052952.524149526</v>
+        <v>7053164</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2535,19 +2294,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2579,15 +2328,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107079100</v>
+        <v>107079088</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2595,34 +2339,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarhön Lien, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447059.5646948483</v>
+        <v>447461</v>
       </c>
       <c r="R18" t="n">
-        <v>7052936.94412514</v>
+        <v>7053147</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2652,19 +2404,14 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2691,15 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107079107</v>
+        <v>107079089</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,34 +2449,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarhön Lien, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447209.1414941939</v>
+        <v>447422</v>
       </c>
       <c r="R19" t="n">
-        <v>7052872.132797293</v>
+        <v>7053067</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2764,24 +2510,14 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>måttligt - rikligt i området</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2808,15 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107079088</v>
+        <v>107079090</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,10 +2587,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447460.6304002258</v>
+        <v>447407</v>
       </c>
       <c r="R20" t="n">
-        <v>7053147.049131247</v>
+        <v>7053034</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2889,19 +2620,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2933,15 +2654,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107079086</v>
+        <v>107079091</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2969,7 +2685,11 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2977,10 +2697,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447521.4769578321</v>
+        <v>447382</v>
       </c>
       <c r="R21" t="n">
-        <v>7053322.742219064</v>
+        <v>7053031</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3010,19 +2730,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3057,12 +2767,7 @@
         <v>107079092</v>
       </c>
       <c r="B22" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3102,10 +2807,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447381.1378359922</v>
+        <v>447381</v>
       </c>
       <c r="R22" t="n">
-        <v>7053029.967409391</v>
+        <v>7053030</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3135,19 +2840,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3179,15 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107079082</v>
+        <v>107079093</v>
       </c>
       <c r="B23" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447168.8873277358</v>
+        <v>447257</v>
       </c>
       <c r="R23" t="n">
-        <v>7052890.608382901</v>
+        <v>7052907</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3256,19 +2946,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3297,6 +2977,222 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>107079094</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hammarhön Lien, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>447236</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7052886</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>107079096</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hammarhön Lien, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>447151</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7052842</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57295-2022 artfynd.xlsx
+++ b/artfynd/A 57295-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079109</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1850978</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079104</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079105</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079106</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079107</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079099</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079100</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079101</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1681,6 +1731,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079102</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1787,6 +1842,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079082</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079083</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2003,6 +2068,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079084</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2113,6 +2183,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079085</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079086</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2325,6 +2405,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079087</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2435,6 +2520,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079088</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2541,6 +2631,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079089</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2651,6 +2746,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079090</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2761,6 +2861,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079091</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2871,6 +2976,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079092</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2977,6 +3087,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079093</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3083,6 +3198,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079094</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3193,8 +3313,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079096</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>